--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260907.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260907.xlsx
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>漢唐</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>250,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>漢唐</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>250,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1657,12 +1657,12 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>上銀</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>上銀</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
